--- a/tame_output/ON/bt/strategyON_20231206.xlsx
+++ b/tame_output/ON/bt/strategyON_20231206.xlsx
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>1.176391346228884</v>
+        <v>1.175841107096891</v>
       </c>
       <c r="E1803" t="n">
-        <v>3.563861950842348</v>
+        <v>3.563641855189551</v>
       </c>
       <c r="F1803" t="n">
         <v>1.44931938054938</v>

--- a/tame_output/ON/bt/strategyON_20231206.xlsx
+++ b/tame_output/ON/bt/strategyON_20231206.xlsx
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.2%</t>
+          <t>449.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.048806209055149</v>
+        <v>3.04880620905515</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227613</v>
+        <v>3.093259956227614</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408316</v>
+        <v>3.069025022408317</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708494</v>
+        <v>3.085392865708495</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968023</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597767</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527686</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844645</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487811</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.14626574482338</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714842</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083875</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666732</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097097</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963478</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742722</v>
+        <v>3.238767863742723</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589522</v>
+        <v>3.260068416589523</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,16 +42979,16 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>2.910034499038135</v>
+        <v>2.910034499038136</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>1.175841107096891</v>
+        <v>1.178546026674774</v>
       </c>
       <c r="E1803" t="n">
-        <v>3.563641855189551</v>
+        <v>3.564723823020704</v>
       </c>
       <c r="F1803" t="n">
         <v>1.44931938054938</v>

--- a/tame_output/ON/bt/strategyON_20231206.xlsx
+++ b/tame_output/ON/bt/strategyON_20231206.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -987,22 +987,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.1%</t>
+          <t>454.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-54.6%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,27 +1145,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>1.178546026674774</v>
+        <v>0.877946092712133</v>
       </c>
       <c r="E1803" t="n">
-        <v>3.564723823020704</v>
+        <v>3.444483849435648</v>
       </c>
       <c r="F1803" t="n">
         <v>1.44931938054938</v>

--- a/tame_output/ON/bt/strategyON_20231206.xlsx
+++ b/tame_output/ON/bt/strategyON_20231206.xlsx
@@ -41806,7 +41806,7 @@
         <v>45214</v>
       </c>
       <c r="B1752" t="n">
-        <v>2.81784116067579</v>
+        <v>2.817841160675789</v>
       </c>
       <c r="C1752" t="n">
         <v>2.953840430523644</v>
@@ -41829,7 +41829,7 @@
         <v>45215</v>
       </c>
       <c r="B1753" t="n">
-        <v>2.855808668290734</v>
+        <v>2.855808668290733</v>
       </c>
       <c r="C1753" t="n">
         <v>2.959094075792072</v>
@@ -41921,7 +41921,7 @@
         <v>45219</v>
       </c>
       <c r="B1757" t="n">
-        <v>2.902669647939157</v>
+        <v>2.902669647939156</v>
       </c>
       <c r="C1757" t="n">
         <v>2.968547780644436</v>
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.912903254947841</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968024</v>
+        <v>3.073923642968023</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066013</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293022</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239775</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597767</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527686</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823381</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714842</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083876</v>
+        <v>3.136752015083875</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666733</v>
+        <v>3.162269743666732</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097098</v>
+        <v>3.163432091097097</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.185514355963478</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
